--- a/Amelia/story/promt_csv/chapter_12/todo.xlsx
+++ b/Amelia/story/promt_csv/chapter_12/todo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DEV\ER\gizmobot\games\visual novels\theCK\Amelia\story\promt_csv\chapter_12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356375A5-F1ED-45B4-A315-136B6F1C5E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350BCC64-2660-4D7B-8023-E344D5F7C187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{350EC80C-6400-4772-B4D0-661B6958D559}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="158">
   <si>
     <t>prompt</t>
   </si>
@@ -89,177 +89,6 @@
     <t>show amelia_greeting_friends</t>
   </si>
   <si>
-    <t>show amelia_sitting_with_friends</t>
-  </si>
-  <si>
-    <t>show group_laughing</t>
-  </si>
-  <si>
-    <t>show amelia_nodding</t>
-  </si>
-  <si>
-    <t>show amelia_blushing</t>
-  </si>
-  <si>
-    <t>show friends_toasting</t>
-  </si>
-  <si>
-    <t>show amelia_emotional</t>
-  </si>
-  <si>
-    <t>show amelia_talking_to_lucas</t>
-  </si>
-  <si>
-    <t>show lucas_confiding</t>
-  </si>
-  <si>
-    <t>show amelia_touched</t>
-  </si>
-  <si>
-    <t>show amelia_hugging_lucas</t>
-  </si>
-  <si>
-    <t>show amelia_talking_to_zara</t>
-  </si>
-  <si>
-    <t>show zara_confiding</t>
-  </si>
-  <si>
-    <t>show amelia_listening</t>
-  </si>
-  <si>
-    <t>show amelia_smiling</t>
-  </si>
-  <si>
-    <t>show zara_hugging_amelia</t>
-  </si>
-  <si>
-    <t>show amelia_talking_to_raj</t>
-  </si>
-  <si>
-    <t>show raj_confiding</t>
-  </si>
-  <si>
-    <t>show group_talking_and_laughing</t>
-  </si>
-  <si>
-    <t>show amelia_and_friends_at_end_of_night</t>
-  </si>
-  <si>
-    <t>show amelia_smiling_content</t>
-  </si>
-  <si>
-    <t>show amelia_walking_home</t>
-  </si>
-  <si>
-    <t>show amelia_smiling_upward</t>
-  </si>
-  <si>
-    <t>show amelia_packing_bag</t>
-  </si>
-  <si>
-    <t>show amelia_meeting_mentor</t>
-  </si>
-  <si>
-    <t>show amelia_smiling_sitting</t>
-  </si>
-  <si>
-    <t>show hawthorne_nodding</t>
-  </si>
-  <si>
-    <t>show amelia_grateful</t>
-  </si>
-  <si>
-    <t>show amelia_with_family</t>
-  </si>
-  <si>
-    <t>show lily_looking_up_to_amelia</t>
-  </si>
-  <si>
-    <t>show amelia_nodding_smile</t>
-  </si>
-  <si>
-    <t>show amelia_laughing</t>
-  </si>
-  <si>
-    <t>show amelia_with_friends</t>
-  </si>
-  <si>
-    <t>show amelia_smiling_at_friends</t>
-  </si>
-  <si>
-    <t>show group_dining</t>
-  </si>
-  <si>
-    <t>show amelia_reflecting_on_growth</t>
-  </si>
-  <si>
-    <t>show lucas_nodding</t>
-  </si>
-  <si>
-    <t>show amelia_talking_to_group</t>
-  </si>
-  <si>
-    <t>show amelia_reflecting_in_room</t>
-  </si>
-  <si>
-    <t>show amelia_journaling</t>
-  </si>
-  <si>
-    <t>show amelia_determined</t>
-  </si>
-  <si>
-    <t>show amelia_sitting_in_garden</t>
-  </si>
-  <si>
-    <t>show amelia_receiving_text</t>
-  </si>
-  <si>
-    <t>show amelia_texting_back</t>
-  </si>
-  <si>
-    <t>show amelia_crying_in_garden</t>
-  </si>
-  <si>
-    <t>show zara</t>
-  </si>
-  <si>
-    <t>show amelia_hugging_zara</t>
-  </si>
-  <si>
-    <t>show amelia_talking_to_professor_hawthorne</t>
-  </si>
-  <si>
-    <t>show amelia_nodding_sadly</t>
-  </si>
-  <si>
-    <t>show amelia_at_memorial</t>
-  </si>
-  <si>
-    <t>show amelia_lying_in_bed</t>
-  </si>
-  <si>
-    <t>show amelia_helping_people</t>
-  </si>
-  <si>
-    <t>show amelia_talking_to_coordinator</t>
-  </si>
-  <si>
-    <t>show amelia_reflecting_at_home</t>
-  </si>
-  <si>
-    <t>show amelia_on_phone_with_sarah</t>
-  </si>
-  <si>
-    <t>show amelia_thankful</t>
-  </si>
-  <si>
-    <t>show amelia_smiling_at_lily</t>
-  </si>
-  <si>
-    <t>show amelia_writing_in_journal</t>
-  </si>
-  <si>
     <t>An 18-year-old girl named Amelia looking at her phone. Amelia has fair skin, long brown hair, and blue eyes. The bedroom is familiar and comfortable. Semi-realistic art style. 16:9 Format</t>
   </si>
   <si>
@@ -494,13 +323,193 @@
     <t>A flashback scene with an 18-year-old girl named Amelia with her friend Sarah in a hospital room. Amelia has fair skin, long brown hair, and blue eyes. Sarah has fair skin, middle short blond hair and blue eyes. The hospital room is somber and emotional. Semi-realistic art style. 16:9 Format</t>
   </si>
   <si>
-    <t>An 18-year-old girl named Amelia at a memorial for her friend Sarah. Amelia has fair skin, long brown hair, and blue eyes. Sarah has fair skin, middle short blond hair and blue eyes. The memorial is somber and reflective. Semi-realistic art style. 16:9 Format</t>
-  </si>
-  <si>
-    <t>An 18-year-old girl named Amelia journaling in her room looking sad an empty. Amelia has fair skin, long brown hair, and blue eyes. The bedroom is familiar and comfortable. Semi-realistic art style. 16:9 Format</t>
-  </si>
-  <si>
-    <t>An 18-year-old girl named Amelia lying in bed crying sad. Amelia has fair skin, long brown hair, and blue eyes. The bedroom is familiar and comfortable. Semi-realistic art style. 16:9 Format</t>
+    <t>amelia_sitting_with_friends</t>
+  </si>
+  <si>
+    <t>group_laughing</t>
+  </si>
+  <si>
+    <t>amelia_nodding</t>
+  </si>
+  <si>
+    <t>amelia_blushing</t>
+  </si>
+  <si>
+    <t>friends_toasting</t>
+  </si>
+  <si>
+    <t>amelia_emotional</t>
+  </si>
+  <si>
+    <t>amelia_talking_to_lucas</t>
+  </si>
+  <si>
+    <t>lucas_confiding</t>
+  </si>
+  <si>
+    <t>amelia_touched</t>
+  </si>
+  <si>
+    <t>amelia_hugging_lucas</t>
+  </si>
+  <si>
+    <t>amelia_talking_to_zara</t>
+  </si>
+  <si>
+    <t>zara_confiding</t>
+  </si>
+  <si>
+    <t>amelia_listening</t>
+  </si>
+  <si>
+    <t>amelia_smiling</t>
+  </si>
+  <si>
+    <t>zara_hugging_amelia</t>
+  </si>
+  <si>
+    <t>amelia_talking_to_raj</t>
+  </si>
+  <si>
+    <t>raj_confiding</t>
+  </si>
+  <si>
+    <t>group_talking_and_laughing</t>
+  </si>
+  <si>
+    <t>amelia_and_friends_at_end_of_night</t>
+  </si>
+  <si>
+    <t>amelia_smiling_content</t>
+  </si>
+  <si>
+    <t>amelia_walking_home</t>
+  </si>
+  <si>
+    <t>amelia_smiling_upward</t>
+  </si>
+  <si>
+    <t>amelia_packing_bag</t>
+  </si>
+  <si>
+    <t>amelia_meeting_mentor</t>
+  </si>
+  <si>
+    <t>amelia_smiling_sitting</t>
+  </si>
+  <si>
+    <t>hawthorne_nodding</t>
+  </si>
+  <si>
+    <t>amelia_grateful</t>
+  </si>
+  <si>
+    <t>amelia_with_family</t>
+  </si>
+  <si>
+    <t>amelia_smiling_warmly</t>
+  </si>
+  <si>
+    <t>lily_looking_up_to_amelia</t>
+  </si>
+  <si>
+    <t>amelia_nodding_smile</t>
+  </si>
+  <si>
+    <t>amelia_laughing</t>
+  </si>
+  <si>
+    <t>amelia_with_friends</t>
+  </si>
+  <si>
+    <t>amelia_smiling_at_friends</t>
+  </si>
+  <si>
+    <t>group_dining</t>
+  </si>
+  <si>
+    <t>amelia_reflecting_on_growth</t>
+  </si>
+  <si>
+    <t>lucas_nodding</t>
+  </si>
+  <si>
+    <t>amelia_talking_to_group</t>
+  </si>
+  <si>
+    <t>amelia_reflecting_in_room</t>
+  </si>
+  <si>
+    <t>amelia_journaling</t>
+  </si>
+  <si>
+    <t>amelia_determined</t>
+  </si>
+  <si>
+    <t>amelia_sitting_in_garden</t>
+  </si>
+  <si>
+    <t>amelia_receiving_text</t>
+  </si>
+  <si>
+    <t>amelia_texting_back</t>
+  </si>
+  <si>
+    <t>amelia_waiting_for_response</t>
+  </si>
+  <si>
+    <t>amelia_crying_in_garden</t>
+  </si>
+  <si>
+    <t>zara</t>
+  </si>
+  <si>
+    <t>amelia_hugging_zara</t>
+  </si>
+  <si>
+    <t>amelia_talking_to_professor_hawthorne</t>
+  </si>
+  <si>
+    <t>amelia_nodding_sadly</t>
+  </si>
+  <si>
+    <t>amelia_at_memorial</t>
+  </si>
+  <si>
+    <t>amelia_lying_in_bed</t>
+  </si>
+  <si>
+    <t>amelia_in_room_preparing</t>
+  </si>
+  <si>
+    <t>amelia_leaving_home</t>
+  </si>
+  <si>
+    <t>amelia_helping_people</t>
+  </si>
+  <si>
+    <t>amelia_talking_to_coordinator</t>
+  </si>
+  <si>
+    <t>amelia_reflecting_at_home</t>
+  </si>
+  <si>
+    <t>amelia_on_phone_with_sarah</t>
+  </si>
+  <si>
+    <t>amelia_grieving_sarah</t>
+  </si>
+  <si>
+    <t>amelia_in_living_room_with_family</t>
+  </si>
+  <si>
+    <t>amelia_thankful</t>
+  </si>
+  <si>
+    <t>amelia_smiling_at_lily</t>
+  </si>
+  <si>
+    <t>amelia_writing_in_journal</t>
   </si>
 </sst>
 </file>
@@ -516,12 +525,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -536,9 +551,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -879,7 +897,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="198.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="118.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -891,996 +909,931 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>17</v>
+      <c r="A17" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>18</v>
+      <c r="A18" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>19</v>
+      <c r="A19" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>20</v>
+      <c r="A20" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>21</v>
+      <c r="A21" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>22</v>
+      <c r="A22" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>23</v>
+      <c r="A23" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>24</v>
+      <c r="A24" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
+      <c r="A25" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
+      <c r="A26" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>27</v>
+      <c r="A27" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>28</v>
+      <c r="A28" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>29</v>
+      <c r="A29" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B29" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B56" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B46" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B53" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B55" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>54</v>
+      <c r="A58" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="B58" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>55</v>
+      <c r="A59" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B60" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>57</v>
+        <v>136</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="B64" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="B65" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="B71" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="B72" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="B73" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="B74" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="B76" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="B78" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="B80" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B81" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="B83" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="B84" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>48</v>
+        <v>127</v>
       </c>
       <c r="B85" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="B86" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="B87" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="B88" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="B89" t="s">
-        <v>122</v>
+        <v>65</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="B90" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="B93" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B95" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="B97" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="B98" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="B99" t="s">
-        <v>141</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="B100" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="B101" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="B102" t="s">
-        <v>144</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B104" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="B105" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="B106" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="B107" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="B108" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="B110" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="B111" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B113" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B114" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B115" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B116" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B117" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B118" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B119" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B120" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B121" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B122" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B123" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B124" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B125" t="s">
-        <v>154</v>
-      </c>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="1"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1"/>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1"/>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="1"/>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1"/>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1"/>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
